--- a/file/temp/DAPC_Microcurriculo.xlsx
+++ b/file/temp/DAPC_Microcurriculo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29121"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29218"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.DAPC\file\temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CAB57FC-828B-4930-8719-B97AB315AA06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9C7CAB5-3F2C-45C0-8EFE-8EEB8228CE67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28898" yWindow="6562" windowWidth="28996" windowHeight="15675" xr2:uid="{57EBF3CA-F4B8-4FD2-936E-633642D9EA06}"/>
+    <workbookView xWindow="57503" yWindow="6413" windowWidth="28994" windowHeight="15675" xr2:uid="{57EBF3CA-F4B8-4FD2-936E-633642D9EA06}"/>
   </bookViews>
   <sheets>
     <sheet name="Actividades" sheetId="1" r:id="rId1"/>

--- a/file/temp/DAPC_Microcurriculo.xlsx
+++ b/file/temp/DAPC_Microcurriculo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29218"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29226"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.DAPC\file\temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9C7CAB5-3F2C-45C0-8EFE-8EEB8228CE67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70CD2756-8C0B-490D-B7D2-DE47A1D40AC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57503" yWindow="6413" windowWidth="28994" windowHeight="15675" xr2:uid="{57EBF3CA-F4B8-4FD2-936E-633642D9EA06}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{57EBF3CA-F4B8-4FD2-936E-633642D9EA06}"/>
   </bookViews>
   <sheets>
     <sheet name="Actividades" sheetId="1" r:id="rId1"/>

--- a/file/temp/DAPC_Microcurriculo.xlsx
+++ b/file/temp/DAPC_Microcurriculo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29226"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29413"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.DAPC\file\temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70CD2756-8C0B-490D-B7D2-DE47A1D40AC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDC0512E-8D95-4A15-8F90-1ED951133AD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{57EBF3CA-F4B8-4FD2-936E-633642D9EA06}"/>
+    <workbookView xWindow="-28898" yWindow="6323" windowWidth="28996" windowHeight="15675" xr2:uid="{57EBF3CA-F4B8-4FD2-936E-633642D9EA06}"/>
   </bookViews>
   <sheets>
     <sheet name="Actividades" sheetId="1" r:id="rId1"/>
